--- a/حركات_الشركات_منظمة/حركات_شركة_WAB.xlsx
+++ b/حركات_الشركات_منظمة/حركات_شركة_WAB.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE846082-DEAC-4459-9150-56C4C8790D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="علاج الطبيعي" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="النظارات" state="visible" r:id="rId5"/>
+    <sheet name="علاج الطبيعي" sheetId="1" r:id="rId1"/>
+    <sheet name="النظارات" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="865">
   <si>
     <t>اسم المريض</t>
   </si>
@@ -56,7 +60,7 @@
     <t xml:space="preserve">10 جلسات </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t> </t>
   </si>
   <si>
     <t>نادية يوسف منصور الشاعري</t>
@@ -104,7 +108,7 @@
     <t>WAB006</t>
   </si>
   <si>
-    <t xml:space="preserve"> 13/4/2026</t>
+    <t> 13/4/2026</t>
   </si>
   <si>
     <t>تركيه  مسعود علي</t>
@@ -116,7 +120,7 @@
     <t>WAB007</t>
   </si>
   <si>
-    <t xml:space="preserve"> 14/4/2026</t>
+    <t> 14/4/2026</t>
   </si>
   <si>
     <t>اوكسجين</t>
@@ -143,7 +147,7 @@
     <t>16/4/2026</t>
   </si>
   <si>
-    <t xml:space="preserve"> 500</t>
+    <t> 500</t>
   </si>
   <si>
     <t>أكسجين</t>
@@ -170,10 +174,10 @@
     <t>WAB011</t>
   </si>
   <si>
-    <t xml:space="preserve"> 22/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> نزار علي العوامي</t>
+    <t> 22/4/2026</t>
+  </si>
+  <si>
+    <t> نزار علي العوامي</t>
   </si>
   <si>
     <t>WAB2025104075</t>
@@ -182,58 +186,58 @@
     <t>WAB012</t>
   </si>
   <si>
-    <t xml:space="preserve"> 24/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 745</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> أطلس</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10 جلسات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> عزيزه عبد الله سعيد</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab2025003214w1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab013</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 26/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 530</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> أوكسجين</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         حسن فرج العشيبي</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab2025003214</t>
+    <t> 24/4/2026</t>
+  </si>
+  <si>
+    <t> 745</t>
+  </si>
+  <si>
+    <t> أطلس</t>
+  </si>
+  <si>
+    <t> 10 جلسات</t>
+  </si>
+  <si>
+    <t> عزيزه عبد الله سعيد</t>
+  </si>
+  <si>
+    <t> wab2025003214w1</t>
+  </si>
+  <si>
+    <t> wab013</t>
+  </si>
+  <si>
+    <t> 26/4/2026</t>
+  </si>
+  <si>
+    <t> 530</t>
+  </si>
+  <si>
+    <t> أوكسجين</t>
+  </si>
+  <si>
+    <t>         حسن فرج العشيبي</t>
+  </si>
+  <si>
+    <t> wab2025003214</t>
   </si>
   <si>
     <t xml:space="preserve">      wab014</t>
   </si>
   <si>
-    <t xml:space="preserve">         500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          أكسجين</t>
+    <t>         500</t>
+  </si>
+  <si>
+    <t>          أكسجين</t>
   </si>
   <si>
     <t xml:space="preserve">        صبريه محمد جابر</t>
   </si>
   <si>
-    <t xml:space="preserve"> WAB2025104101M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      wab015</t>
+    <t> WAB2025104101M1</t>
+  </si>
+  <si>
+    <t>      wab015</t>
   </si>
   <si>
     <t xml:space="preserve">         أوكسجين</t>
@@ -242,10 +246,10 @@
     <t xml:space="preserve">    10 جلسات </t>
   </si>
   <si>
-    <t xml:space="preserve"> نبيهة سالم عبدالله قرقوم</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab2025104561m1</t>
+    <t> نبيهة سالم عبدالله قرقوم</t>
+  </si>
+  <si>
+    <t> wab2025104561m1</t>
   </si>
   <si>
     <t>wab018</t>
@@ -254,10 +258,10 @@
     <t>27/4/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">          اطلس</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> محمد حسين علي الهويدي</t>
+    <t>          اطلس</t>
+  </si>
+  <si>
+    <t> محمد حسين علي الهويدي</t>
   </si>
   <si>
     <t>wab2025009006F1</t>
@@ -275,10 +279,10 @@
     <t>wab2025105945F1</t>
   </si>
   <si>
-    <t xml:space="preserve"> wab020</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 720</t>
+    <t> wab020</t>
+  </si>
+  <si>
+    <t> 720</t>
   </si>
   <si>
     <t>مستشفى بنغازي التخصصي</t>
@@ -290,105 +294,105 @@
     <t>wab021</t>
   </si>
   <si>
-    <t xml:space="preserve"> 200</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> اوكسجين</t>
+    <t> 200</t>
+  </si>
+  <si>
+    <t> اوكسجين</t>
   </si>
   <si>
     <t>14 جلسات</t>
   </si>
   <si>
-    <t xml:space="preserve"> فتحي محمد الجهاني</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab2025628</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab022</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28/4/2026</t>
+    <t> فتحي محمد الجهاني</t>
+  </si>
+  <si>
+    <t> wab2025628</t>
+  </si>
+  <si>
+    <t> wab022</t>
+  </si>
+  <si>
+    <t> 28/4/2026</t>
   </si>
   <si>
     <t xml:space="preserve"> أوكسجين</t>
   </si>
   <si>
-    <t xml:space="preserve"> 14 جلسات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> جميله احميدة فضل الله بن حليم</t>
+    <t> 14 جلسات</t>
+  </si>
+  <si>
+    <t> جميله احميدة فضل الله بن حليم</t>
   </si>
   <si>
     <t>wab2025105180</t>
   </si>
   <si>
-    <t xml:space="preserve"> wab023</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 29/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 50</t>
+    <t> wab023</t>
+  </si>
+  <si>
+    <t> 29/4/2026</t>
+  </si>
+  <si>
+    <t> 50</t>
   </si>
   <si>
     <t>مستشفى ابن سينا التخصصية</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1 جلسات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فاتوره  استرداد</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> منصور ابراهيم منصور</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab2025105157</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> wab024</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 300</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5 جلسات</t>
+    <t> 1 جلسات</t>
+  </si>
+  <si>
+    <t> فاتوره  استرداد</t>
+  </si>
+  <si>
+    <t> منصور ابراهيم منصور</t>
+  </si>
+  <si>
+    <t> wab2025105157</t>
+  </si>
+  <si>
+    <t> wab024</t>
+  </si>
+  <si>
+    <t> 300</t>
+  </si>
+  <si>
+    <t> 5 جلسات</t>
   </si>
   <si>
     <r>
       <rPr>
+        <sz val="14"/>
         <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <sz val="14"/>
-        <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> </t>
+      <t> </t>
     </r>
     <r>
       <rPr>
+        <sz val="14"/>
         <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <sz val="14"/>
-        <rFont val="Aptos Narrow"/>
       </rPr>
       <t>فاتوره استرداد</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> مصطفي حسين مسعود دومة</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> WAB2025106048</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> WAB025</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 30/4/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10</t>
+    <t> مصطفي حسين مسعود دومة</t>
+  </si>
+  <si>
+    <t> WAB2025106048</t>
+  </si>
+  <si>
+    <t> WAB025</t>
+  </si>
+  <si>
+    <t> 30/4/2026</t>
+  </si>
+  <si>
+    <t> 10</t>
   </si>
   <si>
     <t>محمد عبد الونيس  محمد بالروين</t>
@@ -421,10 +425,10 @@
     <t>WAB028</t>
   </si>
   <si>
-    <t xml:space="preserve"> أكسجين</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10جلسات</t>
+    <t> أكسجين</t>
+  </si>
+  <si>
+    <t> 10جلسات</t>
   </si>
   <si>
     <t>انتصار محمد الشريف</t>
@@ -439,7 +443,7 @@
     <t>12 جلسات</t>
   </si>
   <si>
-    <t xml:space="preserve"> سعدية عفون سعد جبريل</t>
+    <t> سعدية عفون سعد جبريل</t>
   </si>
   <si>
     <t>WAB202510424M1</t>
@@ -448,19 +452,19 @@
     <t>WAB030</t>
   </si>
   <si>
-    <t xml:space="preserve"> 10/5/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2250</t>
+    <t> 10/5/2026</t>
+  </si>
+  <si>
+    <t> 2250</t>
   </si>
   <si>
     <t>مصحة منارة المستقبل</t>
   </si>
   <si>
-    <t xml:space="preserve"> 15 جلسات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ابراهيم محمد ابوبكر العبود</t>
+    <t> 15 جلسات</t>
+  </si>
+  <si>
+    <t> ابراهيم محمد ابوبكر العبود</t>
   </si>
   <si>
     <t>WAB2025104893</t>
@@ -469,13 +473,13 @@
     <t>WAB031</t>
   </si>
   <si>
-    <t xml:space="preserve"> 890</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> اكسجين</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> نادية يوسف منصور الشاعري</t>
+    <t> 890</t>
+  </si>
+  <si>
+    <t> اكسجين</t>
+  </si>
+  <si>
+    <t> نادية يوسف منصور الشاعري</t>
   </si>
   <si>
     <t>WAB032</t>
@@ -490,10 +494,10 @@
     <t>WAB033</t>
   </si>
   <si>
-    <t xml:space="preserve"> 11/5/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> امنه محمود المسلاتي</t>
+    <t> 11/5/2026</t>
+  </si>
+  <si>
+    <t> امنه محمود المسلاتي</t>
   </si>
   <si>
     <t>WAB2025003336W1</t>
@@ -502,16 +506,16 @@
     <t>WAB034</t>
   </si>
   <si>
-    <t xml:space="preserve"> صبريه محمد جابر</t>
+    <t> صبريه محمد جابر</t>
   </si>
   <si>
     <t>WAB035</t>
   </si>
   <si>
-    <t xml:space="preserve"> 19/5/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 480</t>
+    <t> 19/5/2026</t>
+  </si>
+  <si>
+    <t> 480</t>
   </si>
   <si>
     <t xml:space="preserve"> اكسجين</t>
@@ -520,7 +524,7 @@
     <t>8 جلسات</t>
   </si>
   <si>
-    <t xml:space="preserve"> احميدين رمضان احميدين</t>
+    <t> احميدين رمضان احميدين</t>
   </si>
   <si>
     <t>WAB2025104277</t>
@@ -529,7 +533,7 @@
     <t>WAB036</t>
   </si>
   <si>
-    <t xml:space="preserve"> هشام يوسف منصور الشاعري</t>
+    <t> هشام يوسف منصور الشاعري</t>
   </si>
   <si>
     <t>WAB2025003378</t>
@@ -538,10 +542,10 @@
     <t>WAB037</t>
   </si>
   <si>
-    <t xml:space="preserve"> اطلس</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ليلي محمد الدوكالي</t>
+    <t> اطلس</t>
+  </si>
+  <si>
+    <t> ليلي محمد الدوكالي</t>
   </si>
   <si>
     <t>WAB2025105949M1</t>
@@ -550,13 +554,13 @@
     <t>WAB038</t>
   </si>
   <si>
-    <t xml:space="preserve"> 20/5/2026</t>
+    <t> 20/5/2026</t>
   </si>
   <si>
     <t xml:space="preserve"> اطلس</t>
   </si>
   <si>
-    <t xml:space="preserve"> حليمة علي  العرفي</t>
+    <t> حليمة علي  العرفي</t>
   </si>
   <si>
     <t>WAB2025105622M1</t>
@@ -574,7 +578,7 @@
     <t>21/5/2026</t>
   </si>
   <si>
-    <t xml:space="preserve"> عادل حفيظ عبدالمالك</t>
+    <t> عادل حفيظ عبدالمالك</t>
   </si>
   <si>
     <t>WAB20259583</t>
@@ -583,10 +587,10 @@
     <t>WAB058</t>
   </si>
   <si>
-    <t xml:space="preserve"> 5/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> عصام الناجي بشير الفريطيس</t>
+    <t> 5/6/2026</t>
+  </si>
+  <si>
+    <t> عصام الناجي بشير الفريطيس</t>
   </si>
   <si>
     <t>WAB2025009603</t>
@@ -595,13 +599,13 @@
     <t>WAB059</t>
   </si>
   <si>
-    <t xml:space="preserve"> 6/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> محمد عبدالمنعم محمد الاحول</t>
+    <t> 6/6/2026</t>
+  </si>
+  <si>
+    <t> 2000</t>
+  </si>
+  <si>
+    <t> محمد عبدالمنعم محمد الاحول</t>
   </si>
   <si>
     <t>WAB2025106113</t>
@@ -610,13 +614,13 @@
     <t>WAB060</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1400</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 20جلسات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> حليمة ضوءاحمد الورفلي</t>
+    <t> 1400</t>
+  </si>
+  <si>
+    <t> 20جلسات</t>
+  </si>
+  <si>
+    <t> حليمة ضوءاحمد الورفلي</t>
   </si>
   <si>
     <t>WAB2025005039</t>
@@ -625,13 +629,13 @@
     <t>WAB061</t>
   </si>
   <si>
-    <t xml:space="preserve"> 8/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1800</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فيزوكير</t>
+    <t> 8/6/2026</t>
+  </si>
+  <si>
+    <t> 1800</t>
+  </si>
+  <si>
+    <t> فيزوكير</t>
   </si>
   <si>
     <t>عزالدين حوسين عبدالهادي</t>
@@ -643,7 +647,7 @@
     <t>WAB062</t>
   </si>
   <si>
-    <t xml:space="preserve"> فرج سعد السماط</t>
+    <t> فرج سعد السماط</t>
   </si>
   <si>
     <t>WAB2025009057</t>
@@ -652,10 +656,10 @@
     <t>WAB063</t>
   </si>
   <si>
-    <t xml:space="preserve"> 10/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> نجمة عبد الحميد بوزريده</t>
+    <t> 10/6/2026</t>
+  </si>
+  <si>
+    <t> نجمة عبد الحميد بوزريده</t>
   </si>
   <si>
     <t>WAB20259015W1</t>
@@ -664,10 +668,10 @@
     <t>WAB064</t>
   </si>
   <si>
-    <t xml:space="preserve">18/6/2026 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> تهاني ابراهيم فركاش</t>
+    <t>18/6/2026 </t>
+  </si>
+  <si>
+    <t> تهاني ابراهيم فركاش</t>
   </si>
   <si>
     <t>WAB20259401</t>
@@ -676,10 +680,10 @@
     <t>WAB065</t>
   </si>
   <si>
-    <t xml:space="preserve"> 14/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1240</t>
+    <t> 14/6/2026</t>
+  </si>
+  <si>
+    <t> 1240</t>
   </si>
   <si>
     <t xml:space="preserve"> ايمان مسعود حمد محمد </t>
@@ -691,16 +695,16 @@
     <t>WAB066</t>
   </si>
   <si>
-    <t xml:space="preserve"> 15/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1050</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> مصحه الحكيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 30 جلسات</t>
+    <t> 15/6/2026</t>
+  </si>
+  <si>
+    <t> 1050</t>
+  </si>
+  <si>
+    <t> مصحه الحكيم</t>
+  </si>
+  <si>
+    <t> 30 جلسات</t>
   </si>
   <si>
     <t>WAB2025106048</t>
@@ -709,7 +713,7 @@
     <t>WAB067</t>
   </si>
   <si>
-    <t xml:space="preserve"> 17/6/2026</t>
+    <t> 17/6/2026</t>
   </si>
   <si>
     <t xml:space="preserve"> معيوفه محمد الجهاني </t>
@@ -721,19 +725,19 @@
     <t>WAB068</t>
   </si>
   <si>
-    <t xml:space="preserve"> غيث بركات عمر الفلاح</t>
+    <t> غيث بركات عمر الفلاح</t>
   </si>
   <si>
     <t>WAB069</t>
   </si>
   <si>
-    <t xml:space="preserve"> 18/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 700</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> محمد جمال محمد الشركسي</t>
+    <t> 18/6/2026</t>
+  </si>
+  <si>
+    <t> 700</t>
+  </si>
+  <si>
+    <t> محمد جمال محمد الشركسي</t>
   </si>
   <si>
     <t>WAB2025105073</t>
@@ -751,13 +755,13 @@
     <t>WAB071</t>
   </si>
   <si>
-    <t xml:space="preserve"> 20/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 20 جلسات</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> رياض محمد عبدالسلام حامد</t>
+    <t> 20/6/2026</t>
+  </si>
+  <si>
+    <t> 20 جلسات</t>
+  </si>
+  <si>
+    <t> رياض محمد عبدالسلام حامد</t>
   </si>
   <si>
     <t>WAB202509803</t>
@@ -766,19 +770,19 @@
     <t>WAB072</t>
   </si>
   <si>
-    <t xml:space="preserve"> 450</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> مصحة المسرة</t>
+    <t> 450</t>
+  </si>
+  <si>
+    <t> مصحة المسرة</t>
   </si>
   <si>
     <t>WAB073</t>
   </si>
   <si>
-    <t xml:space="preserve"> 21/6/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> فتحية عبد الله احمد الشحومي</t>
+    <t> 21/6/2026</t>
+  </si>
+  <si>
+    <t> فتحية عبد الله احمد الشحومي</t>
   </si>
   <si>
     <t>WAB074</t>
@@ -2624,42 +2628,50 @@
   </si>
   <si>
     <t>21/6/2026</t>
-  </si>
-  <si>
-    <t>نورية حمد عبداللطيف</t>
-  </si>
-  <si>
-    <t>WAB2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3046,9 +3058,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J55"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.3984375" customWidth="1"/>
     <col min="2" max="2" width="28.3984375" style="1" customWidth="1"/>
@@ -3062,7 +3074,7 @@
     <col min="10" max="10" width="18.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" s="4" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3091,7 +3103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -3117,7 +3129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
@@ -3143,7 +3155,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
@@ -3169,7 +3181,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>22</v>
       </c>
@@ -3195,7 +3207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
@@ -3221,7 +3233,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
@@ -3247,7 +3259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
@@ -3273,7 +3285,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
@@ -3299,7 +3311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>45</v>
       </c>
@@ -3325,7 +3337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
@@ -3351,7 +3363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>53</v>
       </c>
@@ -3377,7 +3389,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>60</v>
       </c>
@@ -3403,7 +3415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>66</v>
       </c>
@@ -3429,7 +3441,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>71</v>
       </c>
@@ -3455,7 +3467,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>76</v>
       </c>
@@ -3481,7 +3493,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>81</v>
       </c>
@@ -3507,7 +3519,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>85</v>
       </c>
@@ -3533,7 +3545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>60</v>
       </c>
@@ -3559,7 +3571,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>95</v>
       </c>
@@ -3585,7 +3597,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>101</v>
       </c>
@@ -3611,7 +3623,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="18" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
         <v>109</v>
       </c>
@@ -3637,7 +3649,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>115</v>
       </c>
@@ -3663,7 +3675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>120</v>
       </c>
@@ -3689,7 +3701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>124</v>
       </c>
@@ -3715,7 +3727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>127</v>
       </c>
@@ -3741,7 +3753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>132</v>
       </c>
@@ -3767,7 +3779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>136</v>
       </c>
@@ -3793,7 +3805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>143</v>
       </c>
@@ -3819,7 +3831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>148</v>
       </c>
@@ -3845,7 +3857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>150</v>
       </c>
@@ -3871,7 +3883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>154</v>
       </c>
@@ -3897,7 +3909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>157</v>
       </c>
@@ -3923,7 +3935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>163</v>
       </c>
@@ -3949,7 +3961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>166</v>
       </c>
@@ -3975,7 +3987,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>170</v>
       </c>
@@ -4001,7 +4013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>175</v>
       </c>
@@ -4027,7 +4039,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>39</v>
       </c>
@@ -4053,7 +4065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>181</v>
       </c>
@@ -4079,7 +4091,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>185</v>
       </c>
@@ -4105,7 +4117,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>190</v>
       </c>
@@ -4131,7 +4143,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>195</v>
       </c>
@@ -4157,7 +4169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>201</v>
       </c>
@@ -4183,7 +4195,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>204</v>
       </c>
@@ -4209,7 +4221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>208</v>
       </c>
@@ -4235,7 +4247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>212</v>
       </c>
@@ -4261,7 +4273,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>217</v>
       </c>
@@ -4287,7 +4299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>115</v>
       </c>
@@ -4313,7 +4325,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>227</v>
       </c>
@@ -4339,7 +4351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>230</v>
       </c>
@@ -4365,7 +4377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>234</v>
       </c>
@@ -4391,7 +4403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>237</v>
       </c>
@@ -4417,7 +4429,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>242</v>
       </c>
@@ -4443,7 +4455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>148</v>
       </c>
@@ -4469,7 +4481,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>249</v>
       </c>
@@ -4497,14 +4509,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I207"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I203"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.69921875" customWidth="1"/>
     <col min="2" max="2" width="35.09765625" customWidth="1"/>
@@ -4516,7 +4528,7 @@
     <col min="10" max="10" width="19.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4536,7 +4548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>252</v>
       </c>
@@ -4579,7 +4591,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>261</v>
       </c>
@@ -4599,7 +4611,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>263</v>
       </c>
@@ -4619,7 +4631,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>266</v>
       </c>
@@ -4639,7 +4651,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>268</v>
       </c>
@@ -4659,7 +4671,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>271</v>
       </c>
@@ -4679,7 +4691,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>273</v>
       </c>
@@ -4699,7 +4711,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>273</v>
       </c>
@@ -4719,7 +4731,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>276</v>
       </c>
@@ -4739,7 +4751,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>279</v>
       </c>
@@ -4759,7 +4771,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>282</v>
       </c>
@@ -4779,7 +4791,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>285</v>
       </c>
@@ -4799,7 +4811,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>289</v>
       </c>
@@ -4819,7 +4831,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>292</v>
       </c>
@@ -6119,7 +6131,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>472</v>
       </c>
@@ -6139,7 +6151,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>476</v>
       </c>
@@ -6205,7 +6217,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>487</v>
       </c>
@@ -6225,7 +6237,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>491</v>
       </c>
@@ -6245,7 +6257,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>494</v>
       </c>
@@ -6265,7 +6277,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>497</v>
       </c>
@@ -6285,7 +6297,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>500</v>
       </c>
@@ -6305,7 +6317,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>503</v>
       </c>
@@ -6325,7 +6337,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>506</v>
       </c>
@@ -6345,7 +6357,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>509</v>
       </c>
@@ -6365,7 +6377,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>512</v>
       </c>
@@ -6385,7 +6397,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>515</v>
       </c>
@@ -6405,7 +6417,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>518</v>
       </c>
@@ -6425,7 +6437,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>521</v>
       </c>
@@ -8585,43 +8597,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>865</v>
-      </c>
-      <c r="B204" t="s">
-        <v>866</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B205" t="s">
-        <v>866</v>
-      </c>
-      <c r="C205" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B206" t="s">
-        <v>866</v>
-      </c>
-      <c r="C206" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="207" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B207" t="s">
-        <v>866</v>
-      </c>
-      <c r="C207" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>